--- a/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196404_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -737,146 +728,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +861,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,141 +994,118 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1203,146 +1123,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1360,146 +1256,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1517,14 +1389,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1534,128 +1404,107 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1673,146 +1522,122 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1830,146 +1655,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">553
-</t>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">023
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1586
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1987,146 +1788,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2144,92 +1921,77 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
@@ -2239,50 +2001,42 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2300,146 +2054,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2457,146 +2187,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2614,68 +2320,57 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2685,69 +2380,58 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2765,146 +2449,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">412
-</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">014
-</t>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2922,146 +2582,122 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3079,74 +2715,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -3156,68 +2780,57 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">794
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3235,74 +2848,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1254
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3312,68 +2913,57 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3391,146 +2981,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
-</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3548,146 +3114,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3705,38 +3247,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3746,26 +3282,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3775,69 +3307,58 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3855,141 +3376,122 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
+          <t>4179</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4007,128 +3509,107 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
@@ -4138,14 +3619,12 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4163,135 +3642,113 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -4310,110 +3767,92 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0122
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">735
-</t>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -4421,34 +3860,29 @@
           <t>30</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4466,146 +3900,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="R28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4623,68 +4033,57 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -4694,74 +4093,62 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">358
-</t>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4779,74 +4166,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
@@ -4857,62 +4232,52 @@
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4930,141 +4295,118 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">878
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5082,136 +4424,114 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
-</t>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5229,146 +4549,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91619
-</t>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="W33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5386,146 +4682,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5543,146 +4815,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5700,146 +4948,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5857,140 +5081,117 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -6009,146 +5210,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6166,146 +5343,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">715
-</t>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6323,146 +5476,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">653
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6480,136 +5609,114 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">015
-</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">888
-</t>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6627,141 +5734,118 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
@@ -6779,98 +5863,82 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -6880,44 +5948,37 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -6935,8 +5996,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6977,44 +6037,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -7024,98 +6077,82 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7133,146 +6170,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
-</t>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11119
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">654
-</t>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
